--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -37,7 +37,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +52,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -92,13 +87,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -529,153 +521,153 @@
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>WISE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUESDAY</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>MULLINS</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>WISE, CHIASSON</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, CHIASSON</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>CHIASSON</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, MULLINS</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>MULLINS</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>CHIASSON</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>WISE</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>MULLINS</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>MULLINS  (24H)</t>
         </is>
@@ -692,159 +684,159 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>WISE</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>WISE, SAEED</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
           <t>WISE</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, SAEED</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SAEED, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>WISE</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY, SAEED</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>SAEED, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>CHIASSON  (24H)</t>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>WISE  (24H)</t>
         </is>
       </c>
     </row>
@@ -857,161 +849,161 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
           <t>SAEED</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>WISE, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>WISE, SAEED</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>WISE</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY, VIVEKANANDAN</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>SAEED, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>SAEED</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>VIVEKANANDAN</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>WISE, KENNEDY</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>WISE, SAEED</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>SAEED</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>WISE, VIVEKANANDAN</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>WISE, KENNEDY</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>WISE  (24H)</t>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SAEED  (24H)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
@@ -1037,146 +1029,146 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>MONDAY</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="4" t="n">
         <v>23</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>KENNEDY, SHETTY</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>WISE, SHETTY</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>SHETTY</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>WISE, KENNEDY</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY, SHETTY</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>SHETTY</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>WISE</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY, SHETTY</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>KENNEDY</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>KENNEDY  (24H)</t>
         </is>
@@ -1204,15 +1196,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>MONDAY</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>WISE</t>
         </is>
@@ -1222,26 +1214,26 @@
           <t>KENNEDY, VIVEKANANDAN</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>SHETTY</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1272,7 +1264,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1315,7 +1307,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1346,7 +1338,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1377,7 +1369,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -517,13 +517,13 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, CHIASSON</t>
+          <t>MULLINS H, CHIASSON M</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, CHIASSON</t>
+          <t>KENNEDY D, CHIASSON M</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>KENNEDY D, MULLINS H</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -613,17 +613,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -638,17 +638,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>KENNEDY D, MULLINS H</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>MULLINS  (24H)</t>
+          <t>MULLINS H  (24H)</t>
         </is>
       </c>
     </row>
@@ -684,13 +684,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -705,17 +705,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -730,17 +730,17 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -755,17 +755,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SAEED</t>
+          <t>KENNEDY D, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -780,17 +780,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -805,17 +805,17 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -830,13 +830,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>WISE  (24H)</t>
+          <t>WISE J  (24H)</t>
         </is>
       </c>
     </row>
@@ -851,13 +851,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>WISE, VIVEKANANDAN</t>
+          <t>WISE J, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>SAEED, VIVEKANANDAN</t>
+          <t>SAEED U, VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -947,17 +947,17 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>WISE, SAEED</t>
+          <t>WISE J, SAEED U</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -997,13 +997,13 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED U</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>SAEED  (24H)</t>
+          <t>SAEED U  (24H)</t>
         </is>
       </c>
     </row>
@@ -1018,13 +1018,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KENNEDY D, SHETTY K</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1089,17 +1089,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>WISE, SHETTY</t>
+          <t>WISE J, SHETTY K</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1139,17 +1139,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE J, KENNEDY D</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
     </row>
@@ -1164,13 +1164,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>KENNEDY D  (24H)</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1185,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN</t>
+          <t>VIVEKANANDAN S</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>WISE J</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, VIVEKANANDAN</t>
+          <t>KENNEDY D</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>SHETTY</t>
+          <t>SHETTY K</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,13 +521,13 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON M</t>
+          <t>MULLINS</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>WISE J</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -536,19 +540,19 @@
       <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY, MULLINS</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -561,19 +565,19 @@
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -586,19 +590,19 @@
       <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>WISE, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -611,19 +615,19 @@
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -636,40 +640,40 @@
       <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H  (24H)</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>MULLINS  (24H)</t>
         </is>
       </c>
     </row>
@@ -684,13 +688,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>WISE J</t>
+          <t>WISE</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON M</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -703,19 +707,19 @@
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -728,19 +732,19 @@
       <c r="B12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON, WISE</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -753,19 +757,19 @@
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SAEED U</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON, SAEED U</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -778,19 +782,19 @@
       <c r="B14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -803,40 +807,40 @@
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SAEED U</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON, WISE</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>WISE J  (24H)</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>WISE  (24H)</t>
         </is>
       </c>
     </row>
@@ -851,13 +855,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON M</t>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY D</t>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -870,19 +874,19 @@
       <c r="B18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>WISE, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -895,19 +899,19 @@
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -920,19 +924,19 @@
       <c r="B20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY, WISE</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
@@ -945,19 +949,19 @@
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
         </is>
       </c>
     </row>
@@ -970,40 +974,40 @@
       <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, SAEED U</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U  (24H)</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN  (24H)</t>
         </is>
       </c>
     </row>
@@ -1018,13 +1022,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY D</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN S</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1037,19 +1041,19 @@
       <c r="B25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1062,19 +1066,19 @@
       <c r="B26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1087,19 +1091,19 @@
       <c r="B27" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, SHETTY K</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY, VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1112,19 +1116,19 @@
       <c r="B28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1137,40 +1141,40 @@
       <c r="B29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>WISE J, KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN S</t>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>SHETTY, KENNEDY</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY D  (24H)</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1189,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN S</t>
+          <t>SHETTY</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>SHETTY K</t>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
@@ -1204,36 +1208,36 @@
       <c r="B32" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>WISE J</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY D</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY K</t>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>KENNEDY, SHETTY</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1264,7 +1268,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1307,7 +1311,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1338,7 +1342,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1369,7 +1373,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -527,7 +527,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>CHIASSON, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, CHIASSON</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, SAEED U</t>
+          <t>KENNEDY, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -527,7 +527,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, MULLINS</t>
+          <t>KENNEDY, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>WISE, CHIASSON</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY, SAEED U</t>
+          <t>CHIASSON, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -527,7 +527,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>CHIASSON, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, CHIASSON</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MULLINS</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>WISE, MULLINS</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -694,7 +694,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, SAEED U</t>
+          <t>KENNEDY, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -642,17 +642,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, MULLINS</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_November_2026.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
